--- a/topicos_avancado/Arquivos/dados/clientes.xlsx
+++ b/topicos_avancado/Arquivos/dados/clientes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aba1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aba2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aba3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aba4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Aba1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Aba2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Aba3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Aba4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,22 +420,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Idade</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Cidade</t>
         </is>
@@ -558,22 +546,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Idade</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Cidade</t>
         </is>
@@ -684,22 +672,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Idade</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Cidade</t>
         </is>
@@ -810,22 +798,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Idade</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Cidade</t>
         </is>

--- a/topicos_avancado/Arquivos/dados/clientes.xlsx
+++ b/topicos_avancado/Arquivos/dados/clientes.xlsx
@@ -9,8 +9,6 @@
   <sheets>
     <sheet name="Aba1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Aba2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Aba3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Aba4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -660,256 +658,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nome</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Idade</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Cidade</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Juliana</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>26</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Natal</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Sérgio</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>33</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Cuiabá</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Gabriela</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>28</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Vitória</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Eduardo</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>31</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Maceió</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Carla</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>24</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>João Pessoa</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nome</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Idade</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Cidade</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ricardo</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Florianópolis</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Tânia</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>26</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Goiânia</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Elena</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>34</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Aracaju</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Marcos</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>27</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Campo Grande</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Beatriz</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>25</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Belém</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>